--- a/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4108,23 +4108,23 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="J63" t="n">
         <v>1454000</v>
       </c>
       <c r="K63" t="n">
-        <v>2856000</v>
+        <v>3473000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>1,402,000</t>
+          <t>2,019,000</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4277,43 +4277,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>49000</v>
+        <v>41000</v>
       </c>
       <c r="K66" t="n">
         <v>12000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-37,000</t>
+          <t>-29,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4340,43 +4340,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>臻鼎科技控股</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>臻鼎科技控股</t>
+          <t>弘塑科技</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>168000</v>
+        <v>49000</v>
       </c>
       <c r="K67" t="n">
-        <v>110000</v>
+        <v>12000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-58,000</t>
+          <t>-37,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4403,43 +4403,43 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>新代科技</t>
+          <t>健策精密工業</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+0.66%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>83000</v>
+        <v>32000</v>
       </c>
       <c r="K68" t="n">
-        <v>108000</v>
+        <v>49000</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -4461,48 +4461,48 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>臻鼎科技控股</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
+          <t>臻鼎科技控股</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>18000</v>
+        <v>168000</v>
       </c>
       <c r="K69" t="n">
-        <v>31000</v>
+        <v>110000</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>-58,000</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -4529,46 +4529,235 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>56000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>83000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>108000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>8299</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>群聯電子</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>群聯電子</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>0.39%</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>-0.29%</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J73" t="n">
         <v>35000</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K73" t="n">
         <v>20000</v>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>-15,000</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>2026-08-20_00985A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,7 +801,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.50%</t>
+          <t>4.89%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>91000</v>
+        <v>1100000</v>
       </c>
       <c r="K7" t="n">
-        <v>80000</v>
+        <v>1000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>-100,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,55 +879,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>景碩科技</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>514000</v>
+        <v>4000000</v>
       </c>
       <c r="K8" t="n">
-        <v>595000</v>
+        <v>4100000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -937,60 +937,56 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>日月光投</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>日月光投</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.84%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.98%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>+1.14%</t>
-        </is>
-      </c>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>663000</v>
+        <v>1500000</v>
       </c>
       <c r="K9" t="n">
-        <v>753000</v>
+        <v>9000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>-1,491,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,55 +1001,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>3.99%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1942000</v>
+        <v>2300000</v>
       </c>
       <c r="K10" t="n">
-        <v>2293000</v>
+        <v>2400000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>351,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1063,53 +1059,53 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>南亞電路</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>南亞電路</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.09%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>254000</v>
+        <v>3000000</v>
       </c>
       <c r="K11" t="n">
-        <v>249000</v>
+        <v>3250000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-5,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1126,48 +1122,48 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>6.50%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>187000</v>
+        <v>91000</v>
       </c>
       <c r="K12" t="n">
-        <v>209000</v>
+        <v>80000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1179,7 +1175,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1194,55 +1190,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>東元電機</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1454000</v>
+        <v>514000</v>
       </c>
       <c r="K13" t="n">
-        <v>3473000</v>
+        <v>595000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2,019,000</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,60 +1248,60 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>華邦電子</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>7.84%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>447000</v>
+        <v>663000</v>
       </c>
       <c r="K14" t="n">
-        <v>243000</v>
+        <v>753000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-204,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1320,55 +1316,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>50000</v>
+        <v>1942000</v>
       </c>
       <c r="K15" t="n">
-        <v>146000</v>
+        <v>2293000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>351,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1379,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>41000</v>
+        <v>254000</v>
       </c>
       <c r="K16" t="n">
-        <v>12000</v>
+        <v>249000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-29,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1441,429 +1437,3705 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>弘塑科技</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>49000</v>
+        <v>187000</v>
       </c>
       <c r="K17" t="n">
-        <v>12000</v>
+        <v>209000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-37,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>健策精密工業</t>
-        </is>
-      </c>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>健策精密工業</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>+1.08%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>32000</v>
-      </c>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>49000</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>17,000</t>
-        </is>
-      </c>
+        <v>258000</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>臻鼎科技控股</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>臻鼎科技控股</t>
-        </is>
-      </c>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>168000</v>
-      </c>
-      <c r="K19" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-58,000</t>
-        </is>
-      </c>
+        <v>290000</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
+          <t>楠梓電</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.42%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-0.73%</t>
-        </is>
-      </c>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>116000</v>
-      </c>
-      <c r="K20" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>-60,000</t>
-        </is>
-      </c>
+        <v>1181000</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7750</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>新代科技</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>新代科技</t>
-        </is>
-      </c>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.01%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>+0.60%</t>
-        </is>
-      </c>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>83000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
+        <v>236000</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
+          <t>順德</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1.96%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>+0.82%</t>
-        </is>
-      </c>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>18000</v>
-      </c>
-      <c r="K22" t="n">
-        <v>31000</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>13,000</t>
-        </is>
-      </c>
+        <v>788000</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2451</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>創見</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>177000</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>立隆電</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.25%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>518000</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>文曄</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>818000</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>大聯大</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>1930000</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>6257</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>1639000</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>836000</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>6831</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>邁科</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>31000</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>772000</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1758000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2289000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>531,000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-0.90%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>9109000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5285000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-3,824,000</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3.60%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>837000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>844000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>技嘉</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1445000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>355,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>微星</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>5678000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4386000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-1,292,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3.90%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3.87%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>327000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>320000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-7,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>688000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>901000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>213,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2428</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>興勤</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>興勤</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>452000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2356000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1,904,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2455</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1572000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>462,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>962000</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1303000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>341,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2478</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>大毅</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>大毅</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1.16%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>717000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4484000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3,767,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2.79%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2.86%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>248000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>257000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2.62%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2.29%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>417000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>379000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-38,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3090</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>日電貿</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>日電貿</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>532000</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3396000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2,864,000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>2507000</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3432000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>925,000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>+0.23%</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2716000</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3472000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>756,000</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>碩天</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>碩天</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>442000</v>
+      </c>
+      <c r="K48" t="n">
+        <v>603000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>161,000</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1016000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>959000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-57,000</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>37900</v>
+      </c>
+      <c r="K50" t="n">
+        <v>35900</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-2,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5425</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>台半</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.28%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1278000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1544000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>266,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5483</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>中美晶</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>中美晶</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>2484000</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3533000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>1,049,000</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>聖暉*</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>聖暉*</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3.57%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.81%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-2.76%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>2017000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>459000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-1,558,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>6.25%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5.92%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-0.33%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>4025000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3828000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-197,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>226000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>310000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>84,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.10%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>238000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>321000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>83,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6214</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>精誠</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>精誠</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+0.32%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>2638000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3504000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>866,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>450000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>434000</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>-16,000</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6488</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2.26%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2.24%</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1134000</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1117000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>-17,000</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6672</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>騰輝電子-KY</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>406000</v>
+      </c>
+      <c r="K60" t="n">
+        <v>546000</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>140,000</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-0.41%</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>6753000</v>
+      </c>
+      <c r="K61" t="n">
+        <v>2871000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>-3,882,000</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>393000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-307,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-0.70%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-10,000,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-1,500,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-3,000,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K66" t="n">
+        <v>700000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-800,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>510000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>00985A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>東元電機</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>東元電機</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+1.48%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1454000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3473000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2,019,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>447000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>243000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-204,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>146000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>96,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>41000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-0.91%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-37,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>健策精密工業</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>健策精密工業</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>49000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>168000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-58,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>56000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>83000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>108000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>8299</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>群聯電子</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>群聯電子</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>0.68%</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>0.39%</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>-0.29%</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J79" t="n">
         <v>35000</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K79" t="n">
         <v>20000</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>-15,000</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>2026-08-20_00985A_full_holdings.xlsx</t>
         </is>

--- a/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4007,1140 +4007,6 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>0.29%</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>0.16%</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-0.13%</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>700000</v>
-      </c>
-      <c r="K62" t="n">
-        <v>393000</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>-307,000</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>聯電</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-0.70%</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>70000000</v>
-      </c>
-      <c r="K63" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>-10,000,000</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>旺宏</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-0.10%</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="K64" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-1,500,000</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>1.78%</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>1.55%</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-0.23%</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="K65" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>-3,000,000</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2481</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>強茂</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>0.12%</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>0.06%</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-0.06%</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="K66" t="n">
-        <v>700000</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-800,000</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>1.81%</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>+0.22%</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>510000</v>
-      </c>
-      <c r="K67" t="n">
-        <v>550000</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>3.27%</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>3.63%</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>+0.36%</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>1060000</v>
-      </c>
-      <c r="K68" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>40,000</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2026-08-20_00403A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>東元電機</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>東元電機</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>1.01%</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2.49%</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>+1.48%</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>1454000</v>
-      </c>
-      <c r="K69" t="n">
-        <v>3473000</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>2,019,000</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>華邦電子</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>華邦電子</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>0.77%</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>0.42%</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-0.35%</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>447000</v>
-      </c>
-      <c r="K70" t="n">
-        <v>243000</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>-204,000</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>0.33%</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>0.96%</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>+0.63%</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K71" t="n">
-        <v>146000</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>96,000</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>大立光電</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2.11%</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>0.65%</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-1.46%</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>41000</v>
-      </c>
-      <c r="K72" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>-29,000</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>3131</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>弘塑科技</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>弘塑科技</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>1.18%</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-0.91%</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>49000</v>
-      </c>
-      <c r="K73" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>-37,000</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>健策精密工業</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>健策精密工業</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>1.61%</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2.69%</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>+1.08%</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>32000</v>
-      </c>
-      <c r="K74" t="n">
-        <v>49000</v>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>17,000</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>4958</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>臻鼎科技控股</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>臻鼎科技控股</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>0.50%</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>168000</v>
-      </c>
-      <c r="K75" t="n">
-        <v>110000</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>-58,000</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>萬潤科技</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>1.42%</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-0.73%</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>116000</v>
-      </c>
-      <c r="K76" t="n">
-        <v>56000</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>-60,000</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>7750</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>新代科技</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>新代科技</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2.01%</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>2.61%</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>+0.60%</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>83000</v>
-      </c>
-      <c r="K77" t="n">
-        <v>108000</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>25,000</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>7769</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>鴻勁精密</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>1.14%</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>1.96%</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>+0.82%</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>18000</v>
-      </c>
-      <c r="K78" t="n">
-        <v>31000</v>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>13,000</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>群聯電子</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>0.68%</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>0.39%</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-0.29%</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>35000</v>
-      </c>
-      <c r="K79" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>-15,000</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2026-08-20_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4007,6 +4007,447 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1560</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>中砂</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.29%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>700000</v>
+      </c>
+      <c r="K62" t="n">
+        <v>393000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>-307,000</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>4.75%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>-0.70%</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="K63" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-10,000,000</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>旺宏</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-1,500,000</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>-0.23%</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K65" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-3,000,000</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2481</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>強茂</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K66" t="n">
+        <v>700000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-800,000</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>創意</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>510000</v>
+      </c>
+      <c r="K67" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>+0.36%</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>40,000</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-08-21_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,43 +501,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7.19%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5348000</v>
+        <v>294000</v>
       </c>
       <c r="K2" t="n">
-        <v>5148000</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-200,000</t>
+          <t>-293,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -559,48 +559,48 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1000</v>
+        <v>2000000</v>
       </c>
       <c r="K3" t="n">
-        <v>142000</v>
+        <v>1957000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>141,000</t>
+          <t>-43,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -622,48 +622,48 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.55%</t>
+          <t>7.19%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.66%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4615848</v>
+        <v>5348000</v>
       </c>
       <c r="K4" t="n">
-        <v>4671848</v>
+        <v>5148000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>56,000</t>
+          <t>-200,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -685,48 +685,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>833000</v>
+        <v>1000</v>
       </c>
       <c r="K5" t="n">
-        <v>483000</v>
+        <v>142000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-350,000</t>
+          <t>141,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -753,43 +753,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>3.55%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2442000</v>
+        <v>4615848</v>
       </c>
       <c r="K6" t="n">
-        <v>2486000</v>
+        <v>4671848</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>56,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,55 +816,55 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>聯發科技</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.64%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1100000</v>
+        <v>833000</v>
       </c>
       <c r="K7" t="n">
-        <v>1000000</v>
+        <v>483000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>-350,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-20_00991A_full_holdings.xlsx</t>
+          <t>2026-08-20_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,55 +879,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>景碩科技</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4000000</v>
+        <v>2442000</v>
       </c>
       <c r="K8" t="n">
-        <v>4100000</v>
+        <v>2486000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-08-20_00991A_full_holdings.xlsx</t>
+          <t>2026-08-20_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,51 +942,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>日月光投</t>
+          <t>川湖科技</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>6.50%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>5.59%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.91%</t>
+        </is>
+      </c>
       <c r="J9" t="n">
-        <v>1500000</v>
+        <v>91000</v>
       </c>
       <c r="K9" t="n">
-        <v>9000</v>
+        <v>80000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-1,491,000</t>
+          <t>-11,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-20_00991A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1001,55 +1005,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>台燿科技</t>
+          <t>國巨</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2300000</v>
+        <v>514000</v>
       </c>
       <c r="K10" t="n">
-        <v>2400000</v>
+        <v>595000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>81,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-08-20_00991A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1064,48 +1068,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>南亞電路</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>南亞電路</t>
+          <t>台灣積體電路製造</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.09%</t>
+          <t>7.84%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>8.98%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.38%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3000000</v>
+        <v>663000</v>
       </c>
       <c r="K11" t="n">
-        <v>3250000</v>
+        <v>753000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-08-20_00991A_full_holdings.xlsx</t>
+          <t>2026-08-20_00980A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1122,48 +1126,48 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>川湖科技</t>
+          <t>華邦電子</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.50%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.59%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>91000</v>
+        <v>1942000</v>
       </c>
       <c r="K12" t="n">
-        <v>80000</v>
+        <v>2293000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-11,000</t>
+          <t>351,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1185,48 +1189,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>國巨</t>
+          <t>聯發科技</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>4.62%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>514000</v>
+        <v>254000</v>
       </c>
       <c r="K13" t="n">
-        <v>595000</v>
+        <v>249000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>81,000</t>
+          <t>-5,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1253,43 +1257,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>台灣積體電路製造</t>
+          <t>台燿科技</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.84%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8.98%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>663000</v>
+        <v>187000</v>
       </c>
       <c r="K14" t="n">
-        <v>753000</v>
+        <v>209000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1301,189 +1305,135 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>華邦電子</t>
-        </is>
-      </c>
+          <t>2486</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>華邦電子</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1.70%</t>
-        </is>
-      </c>
+          <t>一詮</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.03%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>+0.33%</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>1942000</v>
-      </c>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>2293000</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>351,000</t>
-        </is>
-      </c>
+        <v>950000</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>聯發科技</t>
-        </is>
-      </c>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>聯發科技</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4.90%</t>
-        </is>
-      </c>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.62%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-0.28%</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>254000</v>
-      </c>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>249000</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-5,000</t>
-        </is>
-      </c>
+        <v>516000</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>台燿科技</t>
-        </is>
-      </c>
+          <t>光洋科</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.44%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1.65%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>187000</v>
-      </c>
-      <c r="K17" t="n">
-        <v>209000</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>22,000</t>
-        </is>
-      </c>
+        <v>290000</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-08-20_00980A_full_holdings.xlsx</t>
+          <t>2026-08-20_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
@@ -1495,36 +1445,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>刪除</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>全數賣出</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6472</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>保瑞</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
+          <t>2316</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>楠梓電</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>258000</v>
-      </c>
+      <c r="J18" t="n">
+        <v>1181000</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
@@ -1550,24 +1500,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>光洋科</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>290000</v>
+        <v>236000</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1595,24 +1545,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>楠梓電</t>
+          <t>順德</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>1181000</v>
+        <v>788000</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1640,24 +1590,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>236000</v>
+        <v>177000</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1685,24 +1635,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>順德</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>788000</v>
+        <v>518000</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1730,24 +1680,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>177000</v>
+        <v>818000</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1775,24 +1725,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>518000</v>
+        <v>1930000</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1820,24 +1770,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>818000</v>
+        <v>1639000</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1865,24 +1815,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>1930000</v>
+        <v>836000</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1910,24 +1860,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>1639000</v>
+        <v>300000</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1955,24 +1905,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>836000</v>
+        <v>31000</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2000,24 +1950,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>300000</v>
+        <v>772000</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2035,37 +1985,55 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>鴻勁</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>光寶科</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>光寶科</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.40%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>+0.26%</t>
+        </is>
+      </c>
       <c r="J30" t="n">
-        <v>31000</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+        <v>1758000</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2289000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>531,000</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>2026-08-20_00982A_full_holdings.xlsx</t>
@@ -2080,37 +2048,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>矽創</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>聯電</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>聯電</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.46%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-0.87%</t>
+        </is>
+      </c>
       <c r="J31" t="n">
-        <v>772000</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+        <v>9109000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5285000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-3,824,000</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>2026-08-20_00982A_full_holdings.xlsx</t>
@@ -2135,43 +2121,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1758000</v>
+        <v>837000</v>
       </c>
       <c r="K32" t="n">
-        <v>2289000</v>
+        <v>844000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>531,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2193,48 +2179,48 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.90%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>9109000</v>
+        <v>1445000</v>
       </c>
       <c r="K33" t="n">
-        <v>5285000</v>
+        <v>1800000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-3,824,000</t>
+          <t>355,000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2256,48 +2242,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>837000</v>
+        <v>5678000</v>
       </c>
       <c r="K34" t="n">
-        <v>844000</v>
+        <v>4386000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>-1,292,000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2319,48 +2305,48 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>3.90%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>3.73%</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1445000</v>
+        <v>327000</v>
       </c>
       <c r="K35" t="n">
-        <v>1800000</v>
+        <v>320000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>355,000</t>
+          <t>-7,000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2382,48 +2368,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>5678000</v>
+        <v>688000</v>
       </c>
       <c r="K36" t="n">
-        <v>4386000</v>
+        <v>901000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-1,292,000</t>
+          <t>213,000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2445,48 +2431,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>327000</v>
+        <v>452000</v>
       </c>
       <c r="K37" t="n">
-        <v>320000</v>
+        <v>2356000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-7,000</t>
+          <t>1,904,000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2513,43 +2499,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>688000</v>
+        <v>1110000</v>
       </c>
       <c r="K38" t="n">
-        <v>901000</v>
+        <v>1572000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>213,000</t>
+          <t>462,000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2576,17 +2562,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>興勤</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2596,23 +2582,23 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>452000</v>
+        <v>962000</v>
       </c>
       <c r="K39" t="n">
-        <v>2356000</v>
+        <v>1303000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>1,904,000</t>
+          <t>341,000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2639,43 +2625,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>1110000</v>
+        <v>717000</v>
       </c>
       <c r="K40" t="n">
-        <v>1572000</v>
+        <v>4484000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>462,000</t>
+          <t>3,767,000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2702,43 +2688,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>962000</v>
+        <v>248000</v>
       </c>
       <c r="K41" t="n">
-        <v>1303000</v>
+        <v>257000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>341,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2760,48 +2746,48 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>717000</v>
+        <v>417000</v>
       </c>
       <c r="K42" t="n">
-        <v>4484000</v>
+        <v>379000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>3,767,000</t>
+          <t>-38,000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2828,43 +2814,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>248000</v>
+        <v>532000</v>
       </c>
       <c r="K43" t="n">
-        <v>257000</v>
+        <v>3396000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>2,864,000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -2886,48 +2872,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>417000</v>
+        <v>2507000</v>
       </c>
       <c r="K44" t="n">
-        <v>379000</v>
+        <v>3432000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-38,000</t>
+          <t>925,000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -2949,48 +2935,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>532000</v>
+        <v>4780000</v>
       </c>
       <c r="K45" t="n">
-        <v>3396000</v>
+        <v>3985000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2,864,000</t>
+          <t>-795,000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3017,43 +3003,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2507000</v>
+        <v>2716000</v>
       </c>
       <c r="K46" t="n">
-        <v>3432000</v>
+        <v>3472000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>925,000</t>
+          <t>756,000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3080,43 +3066,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2716000</v>
+        <v>442000</v>
       </c>
       <c r="K47" t="n">
-        <v>3472000</v>
+        <v>603000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>756,000</t>
+          <t>161,000</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3138,48 +3124,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>442000</v>
+        <v>1016000</v>
       </c>
       <c r="K48" t="n">
-        <v>603000</v>
+        <v>959000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>161,000</t>
+          <t>-57,000</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3206,43 +3192,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>1016000</v>
+        <v>37900</v>
       </c>
       <c r="K49" t="n">
-        <v>959000</v>
+        <v>35900</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-57,000</t>
+          <t>-2,000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3264,48 +3250,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>37900</v>
+        <v>1278000</v>
       </c>
       <c r="K50" t="n">
-        <v>35900</v>
+        <v>1544000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-2,000</t>
+          <t>266,000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3332,43 +3318,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>台半</t>
+          <t>中美晶</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1278000</v>
+        <v>2484000</v>
       </c>
       <c r="K51" t="n">
-        <v>1544000</v>
+        <v>3533000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>266,000</t>
+          <t>1,049,000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3390,48 +3376,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>中美晶</t>
+          <t>聖暉*</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>2484000</v>
+        <v>2017000</v>
       </c>
       <c r="K52" t="n">
-        <v>3533000</v>
+        <v>459000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>1,049,000</t>
+          <t>-1,558,000</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3458,43 +3444,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>聖暉*</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>6.25%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>5.98%</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>2017000</v>
+        <v>4025000</v>
       </c>
       <c r="K53" t="n">
-        <v>459000</v>
+        <v>3828000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-1,558,000</t>
+          <t>-197,000</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -3516,48 +3502,48 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>4025000</v>
+        <v>226000</v>
       </c>
       <c r="K54" t="n">
-        <v>3828000</v>
+        <v>310000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-197,000</t>
+          <t>84,000</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3584,17 +3570,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3604,23 +3590,23 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>226000</v>
+        <v>238000</v>
       </c>
       <c r="K55" t="n">
-        <v>310000</v>
+        <v>321000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>84,000</t>
+          <t>83,000</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3647,43 +3633,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>238000</v>
+        <v>2638000</v>
       </c>
       <c r="K56" t="n">
-        <v>321000</v>
+        <v>3504000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>83,000</t>
+          <t>866,000</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3705,48 +3691,48 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2638000</v>
+        <v>450000</v>
       </c>
       <c r="K57" t="n">
-        <v>3504000</v>
+        <v>434000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>866,000</t>
+          <t>-16,000</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -3773,43 +3759,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>450000</v>
+        <v>1134000</v>
       </c>
       <c r="K58" t="n">
-        <v>434000</v>
+        <v>1117000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-16,000</t>
+          <t>-17,000</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -3831,48 +3817,48 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1134000</v>
+        <v>1440000</v>
       </c>
       <c r="K59" t="n">
-        <v>1117000</v>
+        <v>1650000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-17,000</t>
+          <t>210,000</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -3919,12 +3905,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -4108,12 +4094,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -4171,12 +4157,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -4234,12 +4220,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4297,23 +4283,23 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="J66" t="n">
         <v>1500000</v>
       </c>
       <c r="K66" t="n">
-        <v>700000</v>
+        <v>1000</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-800,000</t>
+          <t>-1,499,000</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4360,23 +4346,23 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="J67" t="n">
         <v>510000</v>
       </c>
       <c r="K67" t="n">
-        <v>550000</v>
+        <v>610000</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -4423,12 +4409,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -4445,6 +4431,762 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6274</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1.48%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>120,000</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08-20_00403A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>東元電機</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>東元電機</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2.49%</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>+1.48%</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1454000</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3473000</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2,019,000</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>華邦電子</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.77%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0.42%</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>447000</v>
+      </c>
+      <c r="K71" t="n">
+        <v>243000</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-204,000</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2395</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>研華</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>0.96%</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>+0.63%</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K72" t="n">
+        <v>146000</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>96,000</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>大立光電</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2.11%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>41000</v>
+      </c>
+      <c r="K73" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-29,000</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3131</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>弘塑科技</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-0.91%</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>49000</v>
+      </c>
+      <c r="K74" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-37,000</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>健策精密工業</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>健策精密工業</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.69%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>32000</v>
+      </c>
+      <c r="K75" t="n">
+        <v>49000</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>17,000</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>臻鼎科技控股</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-0.28%</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>168000</v>
+      </c>
+      <c r="K76" t="n">
+        <v>110000</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-58,000</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>萬潤科技</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>-0.73%</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>116000</v>
+      </c>
+      <c r="K77" t="n">
+        <v>56000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-60,000</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>新代科技</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2.61%</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>+0.60%</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>83000</v>
+      </c>
+      <c r="K78" t="n">
+        <v>108000</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>鴻勁精密</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K79" t="n">
+        <v>31000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>群聯電子</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>-0.29%</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>35000</v>
+      </c>
+      <c r="K80" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-15,000</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2026-08-20_00985A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
